--- a/Monthly warehouse expenses.xlsx
+++ b/Monthly warehouse expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karishma.das\Documents\CJ DARCL\Operations\Monthly Opex Expenses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26B52E0-C1DA-4EC4-A46A-363D0028F6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A06C0E5-493B-4AF9-9FDB-1ABBB496D118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD753405-8938-40ED-BF9C-A6CE89EB6A85}"/>
   </bookViews>
@@ -493,7 +493,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -770,12 +770,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -920,6 +933,12 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1421,8 +1440,8 @@
       <c r="E3" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>25</v>
+      <c r="F3" s="49" t="s">
+        <v>44</v>
       </c>
       <c r="G3" s="19">
         <v>125437</v>
@@ -1488,7 +1507,7 @@
         <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G4" s="3">
         <v>528210</v>
@@ -1554,7 +1573,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G5" s="3">
         <v>85998</v>
@@ -1618,7 +1637,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G6" s="3">
         <v>49984</v>
@@ -1682,7 +1701,7 @@
         <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G7" s="3">
         <v>180943</v>
@@ -1746,7 +1765,7 @@
         <v>34</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3">
         <v>3335391</v>
@@ -1812,7 +1831,7 @@
         <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3">
         <v>11962</v>
@@ -1874,7 +1893,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3">
         <v>211637</v>
@@ -1940,7 +1959,7 @@
         <v>24</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3">
         <v>100834</v>
@@ -2004,7 +2023,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3">
         <v>22003</v>
@@ -2046,7 +2065,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3">
         <v>164650</v>
@@ -2109,8 +2128,8 @@
       <c r="E14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>25</v>
+      <c r="F14" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G14" s="1">
         <v>223959</v>
@@ -2174,7 +2193,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G15" s="3">
         <v>15051621</v>
@@ -2238,7 +2257,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G16" s="3">
         <v>1863671</v>
@@ -2302,7 +2321,7 @@
         <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G17" s="3">
         <v>115986</v>
@@ -3864,7 +3883,7 @@
       <c r="E42" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="F42" s="36" t="s">
+      <c r="F42" s="31" t="s">
         <v>66</v>
       </c>
       <c r="G42" s="37">
@@ -3928,8 +3947,8 @@
       <c r="E43" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>25</v>
+      <c r="F43" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G43" s="10">
         <v>129180</v>
@@ -3994,8 +4013,8 @@
       <c r="E44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>25</v>
+      <c r="F44" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G44" s="5">
         <v>585427</v>
@@ -4058,8 +4077,8 @@
       <c r="E45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>25</v>
+      <c r="F45" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G45" s="5">
         <v>95403</v>
@@ -4122,8 +4141,8 @@
       <c r="E46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>25</v>
+      <c r="F46" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G46" s="5">
         <v>48935</v>
@@ -4186,8 +4205,8 @@
       <c r="E47" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>25</v>
+      <c r="F47" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G47" s="5">
         <v>185648</v>
@@ -4250,8 +4269,8 @@
       <c r="E48" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>25</v>
+      <c r="F48" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G48" s="5">
         <v>3072714</v>
@@ -4316,8 +4335,8 @@
       <c r="E49" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>25</v>
+      <c r="F49" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G49" s="5">
         <v>0</v>
@@ -4381,7 +4400,7 @@
         <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G50" s="7">
         <v>185051</v>
@@ -4445,7 +4464,7 @@
         <v>24</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G51" s="3">
         <v>106371</v>
@@ -4509,7 +4528,7 @@
         <v>24</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G52" s="5">
         <v>23413</v>
@@ -4551,7 +4570,7 @@
         <v>24</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G53" s="3">
         <v>67999.680000000008</v>
@@ -4614,8 +4633,8 @@
       <c r="E54" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="5" t="s">
-        <v>25</v>
+      <c r="F54" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G54" s="1">
         <v>242279</v>
@@ -4678,8 +4697,8 @@
       <c r="E55" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>44</v>
+      <c r="F55" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G55" s="5">
         <v>14934010</v>
@@ -4742,8 +4761,8 @@
       <c r="E56" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>44</v>
+      <c r="F56" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G56" s="5">
         <v>2466058</v>
@@ -4807,8 +4826,8 @@
       <c r="E57" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>44</v>
+      <c r="F57" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G57" s="5">
         <v>117436</v>
@@ -6359,7 +6378,7 @@
       <c r="E82" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F82" s="28" t="s">
+      <c r="F82" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G82" s="23">
@@ -6423,8 +6442,8 @@
       <c r="E83" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="10" t="s">
-        <v>25</v>
+      <c r="F83" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
@@ -6461,8 +6480,8 @@
       <c r="E84" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F84" s="5" t="s">
-        <v>25</v>
+      <c r="F84" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -6499,8 +6518,8 @@
       <c r="E85" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F85" s="5" t="s">
-        <v>25</v>
+      <c r="F85" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -6537,8 +6556,8 @@
       <c r="E86" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F86" s="5" t="s">
-        <v>25</v>
+      <c r="F86" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -6575,8 +6594,8 @@
       <c r="E87" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F87" s="5" t="s">
-        <v>25</v>
+      <c r="F87" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -6613,8 +6632,8 @@
       <c r="E88" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F88" s="5" t="s">
-        <v>25</v>
+      <c r="F88" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -6651,8 +6670,8 @@
       <c r="E89" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F89" s="5" t="s">
-        <v>25</v>
+      <c r="F89" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -6690,7 +6709,7 @@
         <v>24</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="3"/>
@@ -6728,7 +6747,7 @@
         <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
@@ -6766,7 +6785,7 @@
         <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="5"/>
@@ -6804,7 +6823,7 @@
         <v>24</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
@@ -6841,8 +6860,8 @@
       <c r="E94" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F94" s="5" t="s">
-        <v>25</v>
+      <c r="F94" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="5"/>
@@ -6879,8 +6898,8 @@
       <c r="E95" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F95" s="5" t="s">
-        <v>44</v>
+      <c r="F95" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -6917,8 +6936,8 @@
       <c r="E96" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F96" s="5" t="s">
-        <v>44</v>
+      <c r="F96" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
@@ -6955,8 +6974,8 @@
       <c r="E97" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F97" s="5" t="s">
-        <v>44</v>
+      <c r="F97" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
@@ -7928,7 +7947,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:U122" xr:uid="{3B263073-2BD3-48B4-976A-5AF0F87293C3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/Monthly warehouse expenses.xlsx
+++ b/Monthly warehouse expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karishma.das\Documents\CJ DARCL\Operations\Monthly Opex Expenses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A06C0E5-493B-4AF9-9FDB-1ABBB496D118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392A1485-62CB-4118-8AFC-B5B1F1C00816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD753405-8938-40ED-BF9C-A6CE89EB6A85}"/>
   </bookViews>
@@ -223,9 +223,6 @@
     <t>(All AC Repairing)</t>
   </si>
   <si>
-    <t>EICHER MOTORS LTD (ROYAL ENFIELD)</t>
-  </si>
-  <si>
     <t>GWALIOR</t>
   </si>
   <si>
@@ -401,6 +398,9 @@
   </si>
   <si>
     <t>DISTRIBUTION (ABFRL)</t>
+  </si>
+  <si>
+    <t>ROYAL ENFIELD</t>
   </si>
 </sst>
 </file>
@@ -1441,7 +1441,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="19">
         <v>125437</v>
@@ -1507,7 +1507,7 @@
         <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3">
         <v>528210</v>
@@ -1573,7 +1573,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" s="3">
         <v>85998</v>
@@ -1637,7 +1637,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="3">
         <v>49984</v>
@@ -1692,16 +1692,16 @@
         <v>46113</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="3">
         <v>180943</v>
@@ -1756,16 +1756,16 @@
         <v>46113</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="3">
         <v>3335391</v>
@@ -1807,7 +1807,7 @@
         <v>10000</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U8" s="22">
         <f t="shared" si="1"/>
@@ -1822,16 +1822,16 @@
         <v>46113</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="3">
         <v>11962</v>
@@ -1884,16 +1884,16 @@
         <v>46113</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" s="3">
         <v>211637</v>
@@ -1935,7 +1935,7 @@
         <v>21780</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U10" s="22">
         <f t="shared" si="1"/>
@@ -1950,16 +1950,16 @@
         <v>46113</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11" s="3">
         <v>100834</v>
@@ -2014,16 +2014,16 @@
         <v>46113</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" s="3">
         <v>22003</v>
@@ -2056,16 +2056,16 @@
         <v>46113</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" s="3">
         <v>164650</v>
@@ -2120,16 +2120,16 @@
         <v>46113</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G14" s="1">
         <v>223959</v>
@@ -2184,13 +2184,13 @@
         <v>46113</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>25</v>
@@ -2248,13 +2248,13 @@
         <v>46113</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>25</v>
@@ -2312,13 +2312,13 @@
         <v>46113</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>25</v>
@@ -2379,13 +2379,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="G18" s="3">
         <v>32370</v>
@@ -2440,16 +2440,16 @@
         <v>46113</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="G19" s="3">
         <v>691482</v>
@@ -2485,7 +2485,7 @@
         <v>82961</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U19" s="22">
         <f t="shared" si="1"/>
@@ -2500,16 +2500,16 @@
         <v>46113</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="G20" s="3">
         <v>98281</v>
@@ -2564,16 +2564,16 @@
         <v>46113</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="G21" s="3">
         <v>208964</v>
@@ -2628,16 +2628,16 @@
         <v>46113</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G22" s="3">
         <v>67876</v>
@@ -2671,17 +2671,17 @@
       <c r="B23" s="2">
         <v>46113</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>32</v>
+      <c r="C23" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G23" s="3">
         <v>611412</v>
@@ -2723,7 +2723,7 @@
         <v>11200</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U23" s="22">
         <f t="shared" si="1"/>
@@ -2741,13 +2741,13 @@
         <v>30</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G24" s="3">
         <v>111478</v>
@@ -2802,16 +2802,16 @@
         <v>46113</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G25" s="3">
         <v>111478</v>
@@ -2866,16 +2866,16 @@
         <v>46113</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G26" s="3">
         <v>1856226</v>
@@ -2917,7 +2917,7 @@
         <v>4000</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="U26" s="22">
         <f t="shared" si="1"/>
@@ -2932,16 +2932,16 @@
         <v>46113</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" s="3">
         <v>895563</v>
@@ -2996,16 +2996,16 @@
         <v>46113</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G28" s="3">
         <v>29221</v>
@@ -3058,16 +3058,16 @@
         <v>46113</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G29" s="3">
         <v>101100</v>
@@ -3120,16 +3120,16 @@
         <v>46113</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G30" s="3">
         <v>3638782</v>
@@ -3171,7 +3171,7 @@
         <v>3730</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U30" s="22">
         <f t="shared" si="1"/>
@@ -3186,16 +3186,16 @@
         <v>46113</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31" s="3">
         <f>2869257+118395</f>
@@ -3238,7 +3238,7 @@
         <v>6840</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U31" s="22">
         <f t="shared" si="1"/>
@@ -3253,16 +3253,16 @@
         <v>46113</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G32" s="3">
         <v>3058302</v>
@@ -3304,7 +3304,7 @@
         <v>7296</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="1"/>
@@ -3319,16 +3319,16 @@
         <v>46113</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="G33" s="3">
         <v>75245</v>
@@ -3369,16 +3369,16 @@
         <v>46113</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G34" s="3">
         <v>295888</v>
@@ -3433,16 +3433,16 @@
         <v>46113</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="E35" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G35" s="3">
         <v>269246</v>
@@ -3493,16 +3493,16 @@
         <v>46113</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G36" s="3">
         <v>0</v>
@@ -3557,16 +3557,16 @@
         <v>46113</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G37" s="3">
         <v>208190</v>
@@ -3621,16 +3621,16 @@
         <v>46113</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G38" s="3">
         <v>0</v>
@@ -3685,16 +3685,16 @@
         <v>46113</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G39" s="3">
         <v>1620638</v>
@@ -3749,16 +3749,16 @@
         <v>46113</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G40" s="3">
         <v>57558</v>
@@ -3811,16 +3811,16 @@
         <v>46113</v>
       </c>
       <c r="C41" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="31" t="s">
-        <v>75</v>
-      </c>
       <c r="E41" s="31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G41" s="32">
         <v>873433</v>
@@ -3874,17 +3874,17 @@
       <c r="B42" s="35">
         <v>46113</v>
       </c>
-      <c r="C42" s="36" t="s">
-        <v>32</v>
+      <c r="C42" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G42" s="37">
         <v>481825</v>
@@ -3948,7 +3948,7 @@
         <v>24</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G43" s="10">
         <v>129180</v>
@@ -3990,7 +3990,7 @@
         <v>5000</v>
       </c>
       <c r="T43" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U43" s="22">
         <f t="shared" si="1"/>
@@ -4014,7 +4014,7 @@
         <v>24</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G44" s="5">
         <v>585427</v>
@@ -4078,7 +4078,7 @@
         <v>24</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G45" s="5">
         <v>95403</v>
@@ -4142,7 +4142,7 @@
         <v>24</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G46" s="5">
         <v>48935</v>
@@ -4196,17 +4196,17 @@
       <c r="B47" s="6">
         <v>46143</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="F47" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G47" s="5">
         <v>185648</v>
@@ -4261,16 +4261,16 @@
         <v>46143</v>
       </c>
       <c r="C48" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="E48" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G48" s="5">
         <v>3072714</v>
@@ -4312,7 +4312,7 @@
         <v>2400</v>
       </c>
       <c r="T48" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U48" s="22">
         <f t="shared" si="1"/>
@@ -4327,16 +4327,16 @@
         <v>46143</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G49" s="5">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>46143</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G50" s="7">
         <v>185051</v>
@@ -4455,16 +4455,16 @@
         <v>46143</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G51" s="3">
         <v>106371</v>
@@ -4519,16 +4519,16 @@
         <v>46143</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G52" s="5">
         <v>23413</v>
@@ -4561,16 +4561,16 @@
         <v>46143</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G53" s="3">
         <v>67999.680000000008</v>
@@ -4625,16 +4625,16 @@
         <v>46143</v>
       </c>
       <c r="C54" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="E54" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G54" s="1">
         <v>242279</v>
@@ -4689,13 +4689,13 @@
         <v>46143</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>25</v>
@@ -4753,13 +4753,13 @@
         <v>46143</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>25</v>
@@ -4818,13 +4818,13 @@
         <v>46143</v>
       </c>
       <c r="C57" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="E57" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>25</v>
@@ -4885,13 +4885,13 @@
         <v>30</v>
       </c>
       <c r="D58" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="G58" s="5">
         <v>34740</v>
@@ -4946,16 +4946,16 @@
         <v>46143</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="G59" s="5">
         <v>711568</v>
@@ -4987,7 +4987,7 @@
         <v>375499</v>
       </c>
       <c r="T59" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U59" s="22">
         <f t="shared" si="1"/>
@@ -5002,16 +5002,16 @@
         <v>46143</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D60" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="G60" s="5">
         <v>101954</v>
@@ -5066,16 +5066,16 @@
         <v>46143</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="G61" s="5">
         <v>196032</v>
@@ -5130,16 +5130,16 @@
         <v>46143</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G62" s="8">
         <v>81379</v>
@@ -5171,17 +5171,17 @@
       <c r="B63" s="6">
         <v>46143</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>32</v>
+      <c r="C63" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G63" s="5">
         <v>487232</v>
@@ -5239,13 +5239,13 @@
         <v>30</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G64" s="3">
         <v>111312.5</v>
@@ -5300,16 +5300,16 @@
         <v>46143</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G65" s="3">
         <v>111312.5</v>
@@ -5364,16 +5364,16 @@
         <v>46143</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G66" s="1">
         <v>2032516</v>
@@ -5415,7 +5415,7 @@
         <v>4000</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U66" s="22">
         <f t="shared" si="1"/>
@@ -5430,16 +5430,16 @@
         <v>46143</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G67" s="3">
         <v>970169</v>
@@ -5494,16 +5494,16 @@
         <v>46143</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G68" s="5">
         <v>37905</v>
@@ -5556,16 +5556,16 @@
         <v>46143</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G69" s="5">
         <v>97215</v>
@@ -5618,16 +5618,16 @@
         <v>46143</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G70" s="5">
         <v>3404489</v>
@@ -5680,16 +5680,16 @@
         <v>46143</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G71" s="5">
         <v>2711808</v>
@@ -5731,7 +5731,7 @@
         <v>8630</v>
       </c>
       <c r="T71" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U71" s="22">
         <f t="shared" si="2"/>
@@ -5746,16 +5746,16 @@
         <v>46143</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G72" s="5">
         <v>3728959</v>
@@ -5797,7 +5797,7 @@
         <v>16100</v>
       </c>
       <c r="T72" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U72" s="22">
         <f t="shared" si="2"/>
@@ -5812,16 +5812,16 @@
         <v>46143</v>
       </c>
       <c r="C73" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D73" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="E73" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F73" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="G73" s="3">
         <v>76024</v>
@@ -5861,17 +5861,17 @@
       <c r="B74" s="6">
         <v>46143</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>32</v>
+      <c r="C74" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G74" s="3">
         <v>271547</v>
@@ -5926,16 +5926,16 @@
         <v>46143</v>
       </c>
       <c r="C75" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="E75" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G75" s="3">
         <v>242217</v>
@@ -5986,16 +5986,16 @@
         <v>46143</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G76" s="5">
         <v>0</v>
@@ -6050,16 +6050,16 @@
         <v>46143</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G77" s="7">
         <v>213070</v>
@@ -6114,16 +6114,16 @@
         <v>46143</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G78" s="5">
         <v>0</v>
@@ -6178,16 +6178,16 @@
         <v>46143</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G79" s="3">
         <v>52424</v>
@@ -6242,16 +6242,16 @@
         <v>46143</v>
       </c>
       <c r="C80" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G80" s="3">
         <v>1671529</v>
@@ -6306,16 +6306,16 @@
         <v>46143</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G81" s="3">
         <v>1090864</v>
@@ -6369,17 +6369,17 @@
       <c r="B82" s="27">
         <v>46143</v>
       </c>
-      <c r="C82" s="28" t="s">
-        <v>32</v>
+      <c r="C82" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F82" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G82" s="23">
         <v>489522</v>
@@ -6443,7 +6443,7 @@
         <v>24</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
@@ -6481,7 +6481,7 @@
         <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -6519,7 +6519,7 @@
         <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -6557,7 +6557,7 @@
         <v>24</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -6585,17 +6585,17 @@
       <c r="B87" s="6">
         <v>46174</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D87" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="E87" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E87" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -6624,16 +6624,16 @@
         <v>46174</v>
       </c>
       <c r="C88" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="E88" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -6662,16 +6662,16 @@
         <v>46174</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -6700,16 +6700,16 @@
         <v>46174</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="3"/>
@@ -6738,16 +6738,16 @@
         <v>46174</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
@@ -6776,16 +6776,16 @@
         <v>46174</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="5"/>
@@ -6814,16 +6814,16 @@
         <v>46174</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
@@ -6852,16 +6852,16 @@
         <v>46174</v>
       </c>
       <c r="C94" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D94" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="E94" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="5"/>
@@ -6890,13 +6890,13 @@
         <v>46174</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>25</v>
@@ -6928,13 +6928,13 @@
         <v>46174</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>25</v>
@@ -6966,13 +6966,13 @@
         <v>46174</v>
       </c>
       <c r="C97" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D97" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="E97" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>25</v>
@@ -7007,13 +7007,13 @@
         <v>30</v>
       </c>
       <c r="D98" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="7"/>
@@ -7042,16 +7042,16 @@
         <v>46174</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D99" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
@@ -7080,16 +7080,16 @@
         <v>46174</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D100" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="3"/>
@@ -7118,16 +7118,16 @@
         <v>46174</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D101" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="3"/>
@@ -7156,16 +7156,16 @@
         <v>46174</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
@@ -7193,17 +7193,17 @@
       <c r="B103" s="6">
         <v>46174</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>32</v>
+      <c r="C103" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -7235,13 +7235,13 @@
         <v>30</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E104" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="39"/>
@@ -7270,16 +7270,16 @@
         <v>46174</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G105" s="3"/>
       <c r="H105" s="40"/>
@@ -7308,16 +7308,16 @@
         <v>46174</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G106" s="1"/>
       <c r="H106" s="41"/>
@@ -7346,16 +7346,16 @@
         <v>46174</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E107" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -7384,16 +7384,16 @@
         <v>46174</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="38"/>
@@ -7422,16 +7422,16 @@
         <v>46174</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E109" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="38"/>
@@ -7460,16 +7460,16 @@
         <v>46174</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E110" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="38"/>
@@ -7498,16 +7498,16 @@
         <v>46174</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="8"/>
@@ -7536,16 +7536,16 @@
         <v>46174</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="8"/>
@@ -7574,16 +7574,16 @@
         <v>46174</v>
       </c>
       <c r="C113" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D113" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D113" s="5" t="s">
+      <c r="E113" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
@@ -7611,17 +7611,17 @@
       <c r="B114" s="6">
         <v>46174</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>32</v>
+      <c r="C114" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="3"/>
@@ -7650,16 +7650,16 @@
         <v>46174</v>
       </c>
       <c r="C115" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="E115" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="9"/>
@@ -7688,16 +7688,16 @@
         <v>46174</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="9"/>
@@ -7726,16 +7726,16 @@
         <v>46174</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
@@ -7764,16 +7764,16 @@
         <v>46174</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="9"/>
@@ -7802,16 +7802,16 @@
         <v>46174</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
@@ -7840,16 +7840,16 @@
         <v>46174</v>
       </c>
       <c r="C120" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
@@ -7878,16 +7878,16 @@
         <v>46174</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="1"/>
@@ -7915,17 +7915,17 @@
       <c r="B122" s="27">
         <v>46174</v>
       </c>
-      <c r="C122" s="28" t="s">
-        <v>32</v>
+      <c r="C122" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D122" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E122" s="28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F122" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G122" s="23"/>
       <c r="H122" s="23"/>
